--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/03_PPC3 - Güvenli Lansman ve Güçlendirilmiş Kontrol/EKG-KLT-FRM-35_guclendirilmis_kontrol_kapasite_dogrulamasi_ve_cikis_on.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/03_PPC3 - Güvenli Lansman ve Güçlendirilmiş Kontrol/EKG-KLT-FRM-35_guclendirilmis_kontrol_kapasite_dogrulamasi_ve_cikis_on.xlsx
@@ -1054,7 +1054,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-35&amp;C&amp;"Arial,Regular"&amp;11Güçlendirilmiş Kontrol Kapasite Doğrulaması ve Çıkış Onay Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Kontrol kapsamı ve müşteri çıkış yetkisi korundu; kapasite/fiili hız girişlerinin sayısal geçerliliği eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8213f8ec1b9e45f6"/>
   <x:tableParts count="1">
@@ -1450,7 +1451,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-35&amp;C&amp;"Arial,Regular"&amp;11Güçlendirilmiş Kontrol Kapasite Doğrulaması ve Çıkış Onay Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Kontrol kapsamı ve müşteri çıkış yetkisi korundu; kapasite/fiili hız girişlerinin sayısal geçerliliği eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d29ae5f83a045f8"/>
   <x:tableParts count="1">
@@ -1834,7 +1836,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-35&amp;C&amp;"Arial,Regular"&amp;11Güçlendirilmiş Kontrol Kapasite Doğrulaması ve Çıkış Onay Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Kontrol kapsamı ve müşteri çıkış yetkisi korundu; kapasite/fiili hız girişlerinin sayısal geçerliliği eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bdfa75260014636"/>
   <x:tableParts count="1">
@@ -2113,7 +2116,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-35&amp;C&amp;"Arial,Regular"&amp;11Güçlendirilmiş Kontrol Kapasite Doğrulaması ve Çıkış Onay Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Kontrol kapsamı ve müşteri çıkış yetkisi korundu; kapasite/fiili hız girişlerinin sayısal geçerliliği eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798ecd2aa4b84ad2"/>
   <x:tableParts count="1">
